--- a/4 четверть_12_JavaScript_nodejs_Валидация данных.xlsx
+++ b/4 четверть_12_JavaScript_nodejs_Валидация данных.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE49BFC-1C55-4F4A-BF58-FA0E66D4F20A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A8FB1F-8836-489C-965F-C320C3003C14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-13875" yWindow="-21720" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fastest validation" sheetId="14" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="385">
   <si>
     <t>Урок 1 часть 1</t>
   </si>
@@ -9290,17 +9290,406 @@
 }</t>
     </r>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>this.validatorSheme.validate(Object.assign({}, this.editedUserData)).map(i =&gt; {return i.path;});
+import Schema  from 'validate';</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>export const validatorSheme = new Schema</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">({
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>UserMail</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: {
+       </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> required: true,
+        match: /^(([^&lt;&gt;()\[\]\\.,;:\s@"]+(\.[^&lt;&gt;()\[\]\\.,;:\s@"]+)*)|(".+"))@((\[[0-9]{1,3}\.[0-9]{1,3}\.[0-9]{1,3}\.[0-9]{1,3}\])|(([a-zA-Z\-0-9]+\.)+[a-zA-Z]{2,}))$///^([A-z0-9_\.-]+)@([A-z0-9_\.-]+)\.([A-z\.]{2,6})$/
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    },
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>UserFirstName:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> {
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">        required: true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    },
+   </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> UserFamily:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> {
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">        required: true,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    },
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CloseDate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> {
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">        required: true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    },
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>UserPass:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> {
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">        required: true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    },
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>newPass:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> {
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">        required: false,
+        length: { min: 6, max: 32 },
+        match: /^(?=.*[a-z])(?=.*[A-Z])(?=.*[0-9]).{6,50}\b/
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    },
+   </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> MailDistrib</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: {
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">        required: false,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    }
+</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -9559,9 +9948,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -9572,57 +9961,57 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="4" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="3" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -9631,7 +10020,7 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -9640,19 +10029,22 @@
     <xf numFmtId="49" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -9660,8 +10052,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{7B23FFB3-A72F-409B-B670-C03B7A66220A}"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -10005,7 +10397,7 @@
       <c r="R3" s="1"/>
       <c r="U3" s="1"/>
     </row>
-    <row r="4" spans="1:22" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
         <v>375</v>
@@ -10013,7 +10405,9 @@
       <c r="C4" s="33" t="s">
         <v>377</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="34" t="s">
+        <v>384</v>
+      </c>
       <c r="G4" s="1"/>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
@@ -12554,7 +12948,7 @@
       <c r="V3" s="2"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>

--- a/4 четверть_12_JavaScript_nodejs_Валидация данных.xlsx
+++ b/4 четверть_12_JavaScript_nodejs_Валидация данных.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A8FB1F-8836-489C-965F-C320C3003C14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CAAB441-B75B-45A9-9C8A-8EBFC266FFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-13875" yWindow="-21720" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fastest validation" sheetId="14" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="388">
   <si>
     <t>Урок 1 часть 1</t>
   </si>
@@ -9671,17 +9671,540 @@
 </t>
     </r>
   </si>
+  <si>
+    <t>Большая проблема в сценариях, когда значение должно быть обязательным!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (Array.isArray(validationResult)) {
+        validationResult.forEach(validationItem =&gt; {
+            switch (validationItem.field) {
+                case 'maxId':
+                    if (errorMaxId.isBlank()) {
+                        switch (validationItem.type) {
+                            case 'number':
+                                errorMaxId = "Max ID должен быть числом.";
+                                break;
+                            case 'numberMin':
+   errorMaxId = "Max ID должен быть положительным числом.";
+                                break;
+                            case 'numberInteger':
+   errorMaxId = "Max ID должен быть целым числом.";
+                                break;
+                            case 'required':
+                            case 'numberNotEqual':
+   errorMaxId = "Max ID не может быть пустым.";
+                                break;
+                            default:
+                                break;
+                        }
+                    }
+                    break;
+                default:
+                    break;
+            }
+        })
+    } else {
+        userInputValid = true;
+    }
+    return {
+        userInputValid,
+        errorMaxId
+    }
+};</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">export const checkUserInputIsCorrectHelper = (newMlRcvr, fastestValidator, groupCommunicationChannel) =&gt; {
+    let userInputValid = false;
+    let errorMaxId = "";
+    const schema = {
+        maxId: { 
+            type: "number", </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>//должно быть числом,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ОДНАКО невозможно безопасно передать input (String)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Если преобразовать String в Number, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>то</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'123.'</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> не провалит тест преобразовавшись в </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>123</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+            min: 0, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>//не может быть отрицательным числом</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+            integer: true, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>//не может быть вещественным числом</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>notEqual: 0,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> // исключить 0 (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>для случая, когда передается null</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, который преобразуется в </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>optional: true,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> //должно быть обязательно</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+        }
+    }
+    const checkInputIsValid = fastestValidator.compile(schema);
+    const validationResult = checkInputIsValid({ 
+        </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>maxId:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> /\./i.test(newMlRcvr.MaxId)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ? </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>newMlRcvr.MaxId</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+newMlRcvr.MaxId</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>//костыль для случаев '123.' в 123</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>//если null или имеет точку на конце, то</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>передавать как строку (будет исключение, что может быть только число)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">,
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">иначе передать как число
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    })
+    // console.log(validationResult);</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -9868,6 +10391,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -9948,9 +10491,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -9961,57 +10504,57 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="5" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="4" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -10020,7 +10563,7 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -10029,25 +10572,31 @@
     <xf numFmtId="49" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -10334,7 +10883,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:V188"/>
+  <dimension ref="A2:V189"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
@@ -11307,1260 +11856,1271 @@
         <v>346</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A83" s="2"/>
-      <c r="B83" s="2" t="s">
+    <row r="83" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="B83" s="36" t="s">
+        <v>385</v>
+      </c>
+      <c r="C83" s="35" t="s">
+        <v>387</v>
+      </c>
+      <c r="D83" s="35" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A84" s="2"/>
+      <c r="B84" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C83" s="21" t="s">
+      <c r="C84" s="21" t="s">
         <v>225</v>
       </c>
-      <c r="D83" s="21" t="s">
+      <c r="D84" s="21" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A84" s="24" t="s">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85" s="24" t="s">
         <v>240</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="C85" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D84" s="1" t="s">
+      <c r="D85" s="1" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A85" s="27" t="s">
-        <v>70</v>
-      </c>
-      <c r="B85" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="C85" s="27" t="s">
-        <v>72</v>
-      </c>
-      <c r="D85" s="27"/>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="27" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B86" s="27" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C86" s="27" t="s">
-        <v>241</v>
+        <v>72</v>
       </c>
       <c r="D86" s="27"/>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="27" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B87" s="27" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C87" s="27" t="s">
-        <v>150</v>
+        <v>241</v>
       </c>
       <c r="D87" s="27"/>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="27" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B88" s="27" t="s">
         <v>77</v>
       </c>
       <c r="C88" s="27" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D88" s="27"/>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="27" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B89" s="27" t="s">
         <v>77</v>
       </c>
       <c r="C89" s="27" t="s">
-        <v>242</v>
+        <v>151</v>
       </c>
       <c r="D89" s="27"/>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="27" t="s">
-        <v>243</v>
+        <v>81</v>
       </c>
       <c r="B90" s="27" t="s">
         <v>77</v>
       </c>
       <c r="C90" s="27" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D90" s="27"/>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="27" t="s">
-        <v>83</v>
+        <v>243</v>
       </c>
       <c r="B91" s="27" t="s">
         <v>77</v>
       </c>
       <c r="C91" s="27" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D91" s="27"/>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="27" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B92" s="27" t="s">
         <v>77</v>
       </c>
       <c r="C92" s="27" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D92" s="27"/>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="27" t="s">
-        <v>247</v>
+        <v>87</v>
       </c>
       <c r="B93" s="27" t="s">
         <v>77</v>
       </c>
       <c r="C93" s="27" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D93" s="27"/>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="27" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B94" s="27" t="s">
         <v>77</v>
       </c>
       <c r="C94" s="27" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D94" s="27"/>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="27" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B95" s="27" t="s">
         <v>77</v>
       </c>
       <c r="C95" s="27" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D95" s="27"/>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="27" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B96" s="27" t="s">
         <v>77</v>
       </c>
       <c r="C96" s="27" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D96" s="27"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="27" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B97" s="27" t="s">
         <v>77</v>
       </c>
       <c r="C97" s="27" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D97" s="27"/>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="27" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B98" s="27" t="s">
         <v>77</v>
       </c>
       <c r="C98" s="27" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D98" s="27"/>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="27" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B99" s="27" t="s">
         <v>77</v>
       </c>
       <c r="C99" s="27" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D99" s="27"/>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="27" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B100" s="27" t="s">
         <v>77</v>
       </c>
       <c r="C100" s="27" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D100" s="27"/>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="27" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B101" s="27" t="s">
         <v>77</v>
       </c>
       <c r="C101" s="27" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D101" s="27"/>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="27" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B102" s="27" t="s">
         <v>77</v>
       </c>
       <c r="C102" s="27" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D102" s="27"/>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="27" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B103" s="27" t="s">
         <v>77</v>
       </c>
       <c r="C103" s="27" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D103" s="27"/>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="27" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B104" s="27" t="s">
         <v>77</v>
       </c>
       <c r="C104" s="27" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D104" s="27"/>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="27" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B105" s="27" t="s">
-        <v>272</v>
+        <v>77</v>
       </c>
       <c r="C105" s="27" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D105" s="27"/>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="27" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B106" s="27" t="s">
-        <v>77</v>
+        <v>272</v>
       </c>
       <c r="C106" s="27" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D106" s="27"/>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="27" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B107" s="27" t="s">
         <v>77</v>
       </c>
       <c r="C107" s="27" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D107" s="27"/>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="27" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B108" s="27" t="s">
         <v>77</v>
       </c>
       <c r="C108" s="27" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D108" s="27"/>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="27" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B109" s="27" t="s">
         <v>77</v>
       </c>
       <c r="C109" s="27" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D109" s="27"/>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="27" t="s">
-        <v>91</v>
+        <v>280</v>
       </c>
       <c r="B110" s="27" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="C110" s="27" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D110" s="27"/>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="B111" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="C111" s="27" t="s">
+        <v>282</v>
+      </c>
+      <c r="D111" s="27"/>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A112" s="27" t="s">
         <v>344</v>
       </c>
-      <c r="B111" s="27"/>
-      <c r="C111" s="27" t="s">
+      <c r="B112" s="27"/>
+      <c r="C112" s="27" t="s">
         <v>345</v>
       </c>
-      <c r="D111" s="27" t="s">
+      <c r="D112" s="27" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A112" s="2"/>
-      <c r="B112" s="2" t="s">
+    <row r="113" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A113" s="2"/>
+      <c r="B113" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C112" s="2" t="s">
+      <c r="C113" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D112" s="2" t="s">
+      <c r="D113" s="2" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="113" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="B113" s="2" t="s">
+    <row r="114" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="B114" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C113" s="2" t="s">
+      <c r="C114" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="D113" s="2" t="s">
+      <c r="D114" s="2" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A114" s="24" t="s">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A115" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="C114" s="21" t="s">
+      <c r="C115" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="D114" s="1" t="s">
+      <c r="D115" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A115" s="27" t="s">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A116" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="B115" s="26" t="s">
+      <c r="B116" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="C115" s="28" t="s">
+      <c r="C116" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="D115" s="27"/>
-    </row>
-    <row r="116" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A116" s="27" t="s">
+      <c r="D116" s="27"/>
+    </row>
+    <row r="117" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A117" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="B116" s="26" t="s">
+      <c r="B117" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="C116" s="28" t="s">
+      <c r="C117" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="D116" s="27"/>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A117" s="27" t="s">
+      <c r="D117" s="27"/>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A118" s="27" t="s">
         <v>344</v>
       </c>
-      <c r="B117" s="27"/>
-      <c r="C117" s="27" t="s">
+      <c r="B118" s="27"/>
+      <c r="C118" s="27" t="s">
         <v>345</v>
       </c>
-      <c r="D117" s="27" t="s">
+      <c r="D118" s="27" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="B118" s="2" t="s">
+    <row r="119" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B119" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C118" s="21" t="s">
+      <c r="C119" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="D118" s="21" t="s">
+      <c r="D119" s="21" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="B119" s="2" t="s">
+    <row r="120" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="B120" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C119" s="2" t="s">
+      <c r="C120" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D119" s="1" t="s">
+      <c r="D120" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A120" s="24" t="s">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A121" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="B120" s="1"/>
-      <c r="C120" s="1" t="s">
+      <c r="B121" s="1"/>
+      <c r="C121" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D120" s="1" t="s">
+      <c r="D121" s="1" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A121" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="B121" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="C121" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="D121" s="26"/>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="B122" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="C122" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="D122" s="26"/>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A123" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="B122" s="26" t="s">
+      <c r="B123" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="C122" s="26" t="s">
+      <c r="C123" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="D122" s="26"/>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A123" s="27" t="s">
+      <c r="D123" s="26"/>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A124" s="27" t="s">
         <v>344</v>
       </c>
-      <c r="B123" s="27"/>
-      <c r="C123" s="27" t="s">
+      <c r="B124" s="27"/>
+      <c r="C124" s="27" t="s">
         <v>345</v>
       </c>
-      <c r="D123" s="27" t="s">
+      <c r="D124" s="27" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="B124" s="2" t="s">
+    <row r="125" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="B125" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C124" s="21" t="s">
+      <c r="C125" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="D124" s="21" t="s">
+      <c r="D125" s="21" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A125" s="24" t="s">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A126" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="B126" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C125" s="21" t="s">
+      <c r="C126" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="D125" s="1" t="s">
+      <c r="D126" s="1" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A126" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="B126" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="C126" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="D126" s="26"/>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="B127" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="C127" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="D127" s="26"/>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A128" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="B127" s="26" t="s">
+      <c r="B128" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="C127" s="26" t="s">
+      <c r="C128" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="D127" s="26"/>
-    </row>
-    <row r="128" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A128" s="26" t="s">
+      <c r="D128" s="26"/>
+    </row>
+    <row r="129" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A129" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="B128" s="26" t="s">
+      <c r="B129" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="C128" s="26" t="s">
+      <c r="C129" s="26" t="s">
         <v>120</v>
-      </c>
-      <c r="D128" s="26"/>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A129" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="B129" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="C129" s="26" t="s">
-        <v>123</v>
       </c>
       <c r="D129" s="26"/>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" s="26" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B130" s="26" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C130" s="26" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D130" s="26"/>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="B131" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="C131" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="D131" s="26"/>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A132" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="B131" s="26" t="s">
+      <c r="B132" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="C131" s="26" t="s">
+      <c r="C132" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="D131" s="26"/>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A132" s="27" t="s">
+      <c r="D132" s="26"/>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A133" s="27" t="s">
         <v>344</v>
       </c>
-      <c r="B132" s="27"/>
-      <c r="C132" s="27" t="s">
+      <c r="B133" s="27"/>
+      <c r="C133" s="27" t="s">
         <v>345</v>
       </c>
-      <c r="D132" s="27" t="s">
+      <c r="D133" s="27" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="144" x14ac:dyDescent="0.3">
-      <c r="B133" s="2" t="s">
+    <row r="134" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+      <c r="B134" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C133" s="21" t="s">
+      <c r="C134" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="D133" s="21" t="s">
+      <c r="D134" s="21" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A134" s="24" t="s">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A135" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="B134" s="2" t="s">
+      <c r="B135" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C134" s="21" t="s">
+      <c r="C135" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="D134" s="1" t="s">
+      <c r="D135" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A135" s="26" t="s">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A136" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="B135" s="26" t="s">
+      <c r="B136" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="C135" s="26" t="s">
+      <c r="C136" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="D135" s="26"/>
-    </row>
-    <row r="136" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A136" s="26" t="s">
+      <c r="D136" s="26"/>
+    </row>
+    <row r="137" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A137" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="B136" s="26" t="s">
+      <c r="B137" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="C136" s="26" t="s">
+      <c r="C137" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="D136" s="26"/>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A137" s="27" t="s">
+      <c r="D137" s="26"/>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A138" s="27" t="s">
         <v>344</v>
       </c>
-      <c r="B137" s="27"/>
-      <c r="C137" s="27" t="s">
+      <c r="B138" s="27"/>
+      <c r="C138" s="27" t="s">
         <v>345</v>
       </c>
-      <c r="D137" s="27" t="s">
+      <c r="D138" s="27" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="B138" s="2" t="s">
+    <row r="139" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="B139" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C138" s="21" t="s">
+      <c r="C139" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="D138" s="21" t="s">
+      <c r="D139" s="21" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A139" s="24" t="s">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A140" s="24" t="s">
         <v>141</v>
       </c>
-      <c r="B139" s="2" t="s">
+      <c r="B140" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C139" s="21" t="s">
+      <c r="C140" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="D139" s="1" t="s">
+      <c r="D140" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A140" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="B140" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="C140" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="D140" s="26"/>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" s="26" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B141" s="26" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C141" s="26" t="s">
-        <v>144</v>
+        <v>72</v>
       </c>
       <c r="D141" s="26"/>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="B142" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="C142" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="D142" s="26"/>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A143" s="26" t="s">
         <v>145</v>
       </c>
-      <c r="B142" s="26" t="s">
+      <c r="B143" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="C142" s="26" t="s">
+      <c r="C143" s="26" t="s">
         <v>147</v>
       </c>
-      <c r="D142" s="26"/>
-    </row>
-    <row r="143" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A143" s="26" t="s">
+      <c r="D143" s="26"/>
+    </row>
+    <row r="144" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A144" s="26" t="s">
         <v>148</v>
       </c>
-      <c r="B143" s="26" t="s">
+      <c r="B144" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="C143" s="26" t="s">
+      <c r="C144" s="26" t="s">
         <v>149</v>
-      </c>
-      <c r="D143" s="26"/>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A144" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="B144" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="C144" s="26" t="s">
-        <v>150</v>
       </c>
       <c r="D144" s="26"/>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" s="26" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B145" s="26" t="s">
         <v>77</v>
       </c>
       <c r="C145" s="26" t="s">
+        <v>150</v>
+      </c>
+      <c r="D145" s="26"/>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A146" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B146" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="C146" s="26" t="s">
         <v>151</v>
       </c>
-      <c r="D145" s="26"/>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A146" s="27" t="s">
+      <c r="D146" s="26"/>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A147" s="27" t="s">
         <v>344</v>
       </c>
-      <c r="B146" s="27"/>
-      <c r="C146" s="27" t="s">
+      <c r="B147" s="27"/>
+      <c r="C147" s="27" t="s">
         <v>345</v>
       </c>
-      <c r="D146" s="27" t="s">
+      <c r="D147" s="27" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="B147" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C147" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="D147" s="21" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="B148" s="2" t="s">
         <v>152</v>
       </c>
       <c r="C148" s="31" t="s">
+        <v>154</v>
+      </c>
+      <c r="D148" s="21" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+      <c r="B149" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C149" s="31" t="s">
         <v>373</v>
       </c>
-      <c r="D148" s="21"/>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A149" s="24" t="s">
+      <c r="D149" s="21"/>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A150" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="B149" s="2" t="s">
+      <c r="B150" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C149" s="21" t="s">
+      <c r="C150" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="D149" s="1" t="s">
+      <c r="D150" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A150" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="B150" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="C150" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="D150" s="26"/>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="B151" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="C151" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="D151" s="26"/>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A152" s="26" t="s">
         <v>157</v>
       </c>
-      <c r="B151" s="26" t="s">
+      <c r="B152" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="C151" s="26" t="s">
+      <c r="C152" s="26" t="s">
         <v>158</v>
       </c>
-      <c r="D151" s="26"/>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A152" s="27" t="s">
+      <c r="D152" s="26"/>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A153" s="27" t="s">
         <v>344</v>
       </c>
-      <c r="B152" s="27"/>
-      <c r="C152" s="27" t="s">
+      <c r="B153" s="27"/>
+      <c r="C153" s="27" t="s">
         <v>345</v>
       </c>
-      <c r="D152" s="27" t="s">
+      <c r="D153" s="27" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="B153" s="2" t="s">
+    <row r="154" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="B154" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C153" s="21" t="s">
+      <c r="C154" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="D153" s="21" t="s">
+      <c r="D154" s="21" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A154" s="24" t="s">
+    <row r="155" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A155" s="24" t="s">
         <v>162</v>
       </c>
-      <c r="B154" s="2" t="s">
+      <c r="B155" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C154" s="21" t="s">
+      <c r="C155" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="D154" s="1" t="s">
+      <c r="D155" s="1" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A155" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="B155" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="C155" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="D155" s="26"/>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156" s="26" t="s">
-        <v>170</v>
+        <v>70</v>
       </c>
       <c r="B156" s="26" t="s">
-        <v>171</v>
+        <v>71</v>
       </c>
       <c r="C156" s="26" t="s">
-        <v>172</v>
+        <v>72</v>
       </c>
       <c r="D156" s="26"/>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" s="26" t="s">
+        <v>170</v>
+      </c>
+      <c r="B157" s="26" t="s">
+        <v>171</v>
+      </c>
+      <c r="C157" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="D157" s="26"/>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A158" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="B157" s="26" t="s">
+      <c r="B158" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="C157" s="26" t="s">
+      <c r="C158" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="D157" s="26"/>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A158" s="27" t="s">
+      <c r="D158" s="26"/>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A159" s="27" t="s">
         <v>344</v>
       </c>
-      <c r="B158" s="27"/>
-      <c r="C158" s="27" t="s">
+      <c r="B159" s="27"/>
+      <c r="C159" s="27" t="s">
         <v>345</v>
       </c>
-      <c r="D158" s="27" t="s">
+      <c r="D159" s="27" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="144" x14ac:dyDescent="0.3">
-      <c r="A159" s="1" t="s">
+    <row r="160" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+      <c r="A160" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B159" s="2" t="s">
+      <c r="B160" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C159" s="21" t="s">
+      <c r="C160" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="D159" s="21" t="s">
+      <c r="D160" s="21" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A160" s="1" t="s">
+    <row r="161" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A161" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B160" s="2" t="s">
+      <c r="B161" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C160" s="21" t="s">
+      <c r="C161" s="21" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A161" s="24" t="s">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A162" s="24" t="s">
         <v>176</v>
       </c>
-      <c r="C161" s="21" t="s">
+      <c r="C162" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="D161" s="1" t="s">
+      <c r="D162" s="1" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A162" s="26" t="s">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A163" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="B162" s="26" t="s">
+      <c r="B163" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="C162" s="26" t="s">
+      <c r="C163" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="D162" s="26"/>
-    </row>
-    <row r="163" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A163" s="26" t="s">
+      <c r="D163" s="26"/>
+    </row>
+    <row r="164" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A164" s="26" t="s">
         <v>177</v>
       </c>
-      <c r="B163" s="26" t="s">
+      <c r="B164" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="C163" s="26" t="s">
+      <c r="C164" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="D163" s="26"/>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A164" s="27" t="s">
+      <c r="D164" s="26"/>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A165" s="27" t="s">
         <v>344</v>
       </c>
-      <c r="B164" s="27"/>
-      <c r="C164" s="27" t="s">
+      <c r="B165" s="27"/>
+      <c r="C165" s="27" t="s">
         <v>345</v>
       </c>
-      <c r="D164" s="27" t="s">
+      <c r="D165" s="27" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="165" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="B165" s="2" t="s">
+    <row r="166" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B166" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C165" s="21" t="s">
+      <c r="C166" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="D165" s="21" t="s">
+      <c r="D166" s="21" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="166" spans="1:4" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A166" s="1" t="s">
+    <row r="167" spans="1:4" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A167" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B166" s="2" t="s">
+      <c r="B167" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C166" s="21" t="s">
+      <c r="C167" s="21" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A167" s="24" t="s">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A168" s="24" t="s">
         <v>186</v>
       </c>
-      <c r="C167" s="21" t="s">
+      <c r="C168" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="D167" s="1" t="s">
+      <c r="D168" s="1" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A168" s="27" t="s">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A169" s="27" t="s">
         <v>344</v>
       </c>
-      <c r="B168" s="27"/>
-      <c r="C168" s="27" t="s">
+      <c r="B169" s="27"/>
+      <c r="C169" s="27" t="s">
         <v>345</v>
       </c>
-      <c r="D168" s="27" t="s">
+      <c r="D169" s="27" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="169" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="B169" s="2" t="s">
+    <row r="170" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B170" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C169" s="21" t="s">
+      <c r="C170" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="D169" s="21" t="s">
+      <c r="D170" s="21" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="170" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A170" s="24" t="s">
+    <row r="171" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A171" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="B170" s="2" t="s">
+      <c r="B171" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="C170" s="21" t="s">
+      <c r="C171" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="D170" s="1" t="s">
+      <c r="D171" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A171" s="27" t="s">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A172" s="27" t="s">
         <v>344</v>
       </c>
-      <c r="B171" s="27"/>
-      <c r="C171" s="27" t="s">
+      <c r="B172" s="27"/>
+      <c r="C172" s="27" t="s">
         <v>345</v>
       </c>
-      <c r="D171" s="27" t="s">
+      <c r="D172" s="27" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="172" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="B172" s="2" t="s">
+    <row r="173" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B173" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C172" s="21" t="s">
+      <c r="C173" s="21" t="s">
         <v>201</v>
       </c>
-      <c r="D172" s="21" t="s">
+      <c r="D173" s="21" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A173" s="24" t="s">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A174" s="24" t="s">
         <v>199</v>
       </c>
-      <c r="B173" s="2" t="s">
+      <c r="B174" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C173" s="21" t="s">
+      <c r="C174" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="D173" s="1" t="s">
+      <c r="D174" s="1" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A174" s="27" t="s">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A175" s="27" t="s">
         <v>344</v>
       </c>
-      <c r="B174" s="27"/>
-      <c r="C174" s="27" t="s">
+      <c r="B175" s="27"/>
+      <c r="C175" s="27" t="s">
         <v>345</v>
       </c>
-      <c r="D174" s="27" t="s">
+      <c r="D175" s="27" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="175" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="B175" s="2" t="s">
+    <row r="176" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="B176" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="C175" s="21" t="s">
+      <c r="C176" s="21" t="s">
         <v>312</v>
       </c>
-      <c r="D175" s="21" t="s">
+      <c r="D176" s="21" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A176" s="24" t="s">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A177" s="24" t="s">
         <v>307</v>
       </c>
-      <c r="C176" s="21" t="s">
+      <c r="C177" s="21" t="s">
         <v>308</v>
       </c>
-      <c r="D176" s="1" t="s">
+      <c r="D177" s="1" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A177" s="27" t="s">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A178" s="27" t="s">
         <v>344</v>
       </c>
-      <c r="B177" s="27"/>
-      <c r="C177" s="27" t="s">
+      <c r="B178" s="27"/>
+      <c r="C178" s="27" t="s">
         <v>345</v>
       </c>
-      <c r="D177" s="27" t="s">
+      <c r="D178" s="27" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="178" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="B178" s="2" t="s">
+    <row r="179" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B179" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="C178" s="2" t="s">
+      <c r="C179" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="D178" s="2" t="s">
+      <c r="D179" s="2" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="179" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A179" s="24" t="s">
+    <row r="180" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A180" s="24" t="s">
         <v>313</v>
       </c>
-      <c r="C179" s="21" t="s">
+      <c r="C180" s="21" t="s">
         <v>314</v>
       </c>
-      <c r="D179" s="21" t="s">
+      <c r="D180" s="21" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A180" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="B180" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="C180" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="D180" s="26"/>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="B181" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="C181" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="D181" s="26"/>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A182" s="26" t="s">
         <v>316</v>
       </c>
-      <c r="B181" s="26" t="s">
+      <c r="B182" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="C181" s="26" t="s">
+      <c r="C182" s="26" t="s">
         <v>317</v>
       </c>
-      <c r="D181" s="26"/>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A182" s="27" t="s">
+      <c r="D182" s="26"/>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A183" s="27" t="s">
         <v>344</v>
       </c>
-      <c r="B182" s="27"/>
-      <c r="C182" s="27" t="s">
+      <c r="B183" s="27"/>
+      <c r="C183" s="27" t="s">
         <v>345</v>
       </c>
-      <c r="D182" s="27" t="s">
+      <c r="D183" s="27" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="183" spans="1:4" ht="144" x14ac:dyDescent="0.3">
-      <c r="B183" s="2" t="s">
+    <row r="184" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+      <c r="B184" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="C183" s="21" t="s">
+      <c r="C184" s="21" t="s">
         <v>327</v>
       </c>
-      <c r="D183" s="21" t="s">
+      <c r="D184" s="21" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A184" s="24" t="s">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A185" s="24" t="s">
         <v>318</v>
       </c>
-      <c r="C184" s="21" t="s">
+      <c r="C185" s="21" t="s">
         <v>319</v>
       </c>
-      <c r="D184" s="1" t="s">
+      <c r="D185" s="1" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A185" s="26" t="s">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A186" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="B185" s="26" t="s">
+      <c r="B186" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="C185" s="26" t="s">
+      <c r="C186" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="D185" s="26"/>
-    </row>
-    <row r="186" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A186" s="26" t="s">
+      <c r="D186" s="26"/>
+    </row>
+    <row r="187" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A187" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="B186" s="26" t="s">
+      <c r="B187" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="C186" s="26" t="s">
+      <c r="C187" s="26" t="s">
         <v>323</v>
       </c>
-      <c r="D186" s="26"/>
-    </row>
-    <row r="187" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="B187" s="2" t="s">
+      <c r="D187" s="26"/>
+    </row>
+    <row r="188" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="B188" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="C187" s="21" t="s">
+      <c r="C188" s="21" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="188" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A188" s="21" t="s">
+    <row r="189" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A189" s="21" t="s">
         <v>326</v>
       </c>
-      <c r="B188" s="2" t="s">
+      <c r="B189" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="C188" s="21" t="s">
+      <c r="C189" s="21" t="s">
         <v>324</v>
       </c>
     </row>
@@ -12948,7 +13508,7 @@
       <c r="V3" s="2"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
